--- a/tests/fixtures/analyzer/case_02_cte_basic/execution_tasks.xlsx
+++ b/tests/fixtures/analyzer/case_02_cte_basic/execution_tasks.xlsx
@@ -967,6 +967,7 @@
           <t>tester</t>
         </is>
       </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
@@ -1034,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,30 +1089,6 @@
           <t>是否必填</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>UR002</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P_CYCLE_ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
